--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484201_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484201_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4123</v>
+        <v>5.8616</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1551</v>
+        <v>6.8223</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7428</v>
+        <v>-0.9607</v>
       </c>
       <c r="G2" t="n">
         <v>1.0668</v>
@@ -610,13 +610,13 @@
         <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6278</v>
+        <v>1.0771</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0989</v>
+        <v>0.5683</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7267</v>
+        <v>0.5088</v>
       </c>
       <c r="V2" t="n">
         <v>2.9363</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.267</v>
+        <v>2.8076</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2916</v>
+        <v>2.6961</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0246</v>
+        <v>0.1116</v>
       </c>
       <c r="G3" t="n">
         <v>2.8741</v>
@@ -688,13 +688,13 @@
         <v>0.1953</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.238</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4566</v>
+        <v>-0.0522</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.322</v>
+        <v>-0.1858</v>
       </c>
       <c r="V3" t="n">
         <v>0.953</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1264</v>
+        <v>0.6836</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1014</v>
+        <v>2.4135</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.975</v>
+        <v>-1.7299</v>
       </c>
       <c r="G4" t="n">
         <v>0.1362</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9669</v>
+        <v>0.5241</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3236</v>
+        <v>0.6357</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3567</v>
+        <v>-0.1116</v>
       </c>
       <c r="V4" t="n">
         <v>0.6093</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7075</v>
+        <v>0.4412</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1635</v>
+        <v>1.2241</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4561</v>
+        <v>-0.7829</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3494</v>
@@ -844,13 +844,13 @@
         <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8853</v>
+        <v>0.619</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5668</v>
+        <v>0.6274</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3185</v>
+        <v>-0.0083</v>
       </c>
       <c r="V5" t="n">
         <v>0.953</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2795</v>
+        <v>0.2777</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2765</v>
+        <v>0.4381</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003</v>
+        <v>-0.1604</v>
       </c>
       <c r="G6" t="n">
         <v>0.3969</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3594</v>
+        <v>-0.3612</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1073</v>
+        <v>0.0544</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2521</v>
+        <v>-0.4155</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5718</v>
+        <v>-1.56</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0615</v>
+        <v>-1.3773</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6333</v>
+        <v>-0.1827</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1428</v>
+        <v>-0.5596</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1042</v>
+        <v>-2.7447</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0387</v>
+        <v>2.1851</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0683</v>
+        <v>-0.7398</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6473</v>
+        <v>-1.9814</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7156</v>
+        <v>1.2416</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2111</v>
+        <v>0.1802</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4569</v>
+        <v>-0.7634</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7542</v>
+        <v>0.9435</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0288</v>
+        <v>-0.3673</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9467</v>
+        <v>0.062</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0821</v>
+        <v>-0.4293</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.067</v>
+        <v>0.3436</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2856</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6301</v>
+        <v>-2.6294</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.175</v>
+        <v>0.5759</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.455</v>
+        <v>-3.2052</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5596</v>
+        <v>-3.1428</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7447</v>
+        <v>-2.1042</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1851</v>
+        <v>-1.0387</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7398</v>
+        <v>0.0683</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9814</v>
+        <v>-0.6473</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2416</v>
+        <v>0.7156</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1802</v>
+        <v>-3.2111</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7634</v>
+        <v>-1.4569</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9435</v>
+        <v>-1.7542</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4374</v>
+        <v>0.9712</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2642</v>
+        <v>0.461</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7016</v>
+        <v>0.5102</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3436</v>
+        <v>-0.067</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0664</v>
+        <v>-1.2856</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6107</v>
+        <v>-3.1282</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4865</v>
+        <v>-1.3854</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1241</v>
+        <v>-1.7429</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4544</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5464</v>
+        <v>-0.064</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3548</v>
+        <v>-0.2537</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1916</v>
+        <v>0.1897</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8285</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6351</v>
+        <v>-3.3861</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2811</v>
+        <v>-0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.354</v>
+        <v>-3.1361</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4083</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8315</v>
+        <v>0.4175</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8335</v>
+        <v>0.1975</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0021</v>
+        <v>0.22</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0047</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6771</v>
+        <v>-5.0949</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6449</v>
+        <v>-3.0899</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0322</v>
+        <v>-2.005</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9796</v>
@@ -1312,13 +1312,13 @@
         <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6317</v>
+        <v>0.2139</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6219</v>
+        <v>0.1769</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0098</v>
+        <v>0.037</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3991</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.332100000000001</v>
+        <v>-5.7269</v>
       </c>
       <c r="E12" t="n">
-        <v>7.462100000000001</v>
+        <v>8.067399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.7941</v>
+        <v>-13.7942</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4201</v>
@@ -1390,10 +1390,10 @@
         <v>3.9068</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1871</v>
+        <v>2.7923</v>
       </c>
       <c r="T12" t="n">
-        <v>1.872100000000001</v>
+        <v>2.4773</v>
       </c>
       <c r="U12" t="n">
         <v>0.3152</v>
@@ -1405,7 +1405,7 @@
         <v>7.6467</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.9323</v>
+        <v>-4.932300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5771</v>
+        <v>5.373</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9812</v>
+        <v>6.5879</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4041</v>
+        <v>-1.2149</v>
       </c>
       <c r="G13" t="n">
         <v>2.7404</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.554</v>
+        <v>-0.758</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2105</v>
+        <v>-0.6038</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3435</v>
+        <v>-0.1542</v>
       </c>
       <c r="V13" t="n">
         <v>1.8279</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2719</v>
+        <v>1.9719</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8126</v>
+        <v>1.7489</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4593</v>
+        <v>0.223</v>
       </c>
       <c r="G14" t="n">
-        <v>0.094</v>
+        <v>0.5847</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2829</v>
+        <v>2.0683</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1889</v>
+        <v>-1.4836</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3687</v>
+        <v>0.9248</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2878</v>
+        <v>1.5989</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2747</v>
+        <v>-0.3401</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0049</v>
+        <v>0.4694</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2698</v>
+        <v>-0.8095</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5099</v>
+        <v>0.7463</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1666</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3433</v>
+        <v>0.1994</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W14" t="n">
         <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1261</v>
+        <v>1.5935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7845</v>
+        <v>2.3667</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6584</v>
+        <v>-0.7731</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3527</v>
+        <v>2.3375</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1059</v>
+        <v>2.4318</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7533</v>
+        <v>-0.0944</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2931</v>
+        <v>2.4875</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6413</v>
+        <v>1.9071</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3482</v>
+        <v>0.5803</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0595</v>
+        <v>-0.15</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4646</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>-0.6747</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2107</v>
+        <v>0.3845</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4914</v>
+        <v>0.2113</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2807</v>
+        <v>0.1732</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>-2.1052</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8451</v>
+        <v>1.5882</v>
       </c>
       <c r="E16" t="n">
-        <v>2.67</v>
+        <v>1.9756</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8249</v>
+        <v>-0.3874</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3375</v>
+        <v>1.3527</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4318</v>
+        <v>3.1059</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0944</v>
+        <v>-1.7533</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4875</v>
+        <v>1.2931</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9071</v>
+        <v>2.6413</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5803</v>
+        <v>-1.3482</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.15</v>
+        <v>0.0595</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4646</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6747</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6361</v>
+        <v>0.6727</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5147</v>
+        <v>0.6824</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1215</v>
+        <v>-0.0097</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1052</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7731</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8177</v>
+        <v>1.4746</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6478</v>
+        <v>1.2059</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1699</v>
+        <v>0.2687</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5847</v>
+        <v>0.094</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0683</v>
+        <v>0.2829</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4836</v>
+        <v>-0.1889</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9248</v>
+        <v>0.3687</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5989</v>
+        <v>0.2878</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3401</v>
+        <v>-0.2747</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4694</v>
+        <v>-0.0049</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8095</v>
+        <v>-0.2698</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5921</v>
+        <v>0.7126</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4458</v>
+        <v>0.5599</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1463</v>
+        <v>0.1527</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.2218</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1573</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2636</v>
+        <v>1.129</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1682</v>
+        <v>-0.412</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4249</v>
+        <v>-0.2239</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5931999999999999</v>
+        <v>-0.1881</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5415</v>
+        <v>-0.0622</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0038</v>
+        <v>-0.5488</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5377</v>
+        <v>0.4866</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3733</v>
+        <v>-0.3498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4287</v>
+        <v>0.3249</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9445</v>
+        <v>-0.6747</v>
       </c>
       <c r="P18" t="n">
         <v>1.3674</v>
@@ -1858,28 +1858,28 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3648</v>
+        <v>0.5984</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0522</v>
+        <v>0.4871</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3126</v>
+        <v>0.1113</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
         <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6553</v>
+        <v>1.0025</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3116</v>
+        <v>1.1573</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9669</v>
+        <v>-0.1547</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.412</v>
+        <v>0.1682</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2239</v>
+        <v>-0.4249</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1881</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0622</v>
+        <v>1.5415</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5488</v>
+        <v>0.0038</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4866</v>
+        <v>1.5377</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3498</v>
+        <v>-1.3733</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3249</v>
+        <v>-0.4287</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6747</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
         <v>1.3674</v>
@@ -1936,22 +1936,22 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0319</v>
+        <v>-0.2559</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0522</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0507</v>
+        <v>-0.2037</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
         <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1657</v>
+        <v>0.403</v>
       </c>
       <c r="E20" t="n">
-        <v>1.117</v>
+        <v>1.2182</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9513</v>
+        <v>-0.8152</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8453</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4017</v>
+        <v>0.639</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4458</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V20" t="n">
         <v>1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1079</v>
+        <v>-0.8525</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5513</v>
+        <v>0.7536</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6592</v>
+        <v>-1.6061</v>
       </c>
       <c r="G21" t="n">
         <v>1.2362</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2073</v>
+        <v>-0.952</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9684</v>
+        <v>-0.7661</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.239</v>
+        <v>-0.1858</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9414</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1115</v>
+        <v>-1.1388</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0181</v>
+        <v>-1.0177</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1296</v>
+        <v>-0.1211</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.05</v>
+        <v>-1.4222</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7463</v>
+        <v>0.7355</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7963</v>
+        <v>-2.1577</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3283</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>1.045</v>
+        <v>0.4707</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2833</v>
+        <v>-1.3482</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3783</v>
+        <v>-0.5447</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2988</v>
+        <v>0.2648</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-0.8095</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8661</v>
+        <v>-0.3026</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4153</v>
+        <v>-0.1402</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4508</v>
+        <v>-0.1624</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.787</v>
+        <v>-1.2255</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4222</v>
+        <v>-0.2852</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3648</v>
+        <v>-0.9403</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4222</v>
+        <v>-0.05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7355</v>
+        <v>0.7463</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1577</v>
+        <v>-0.7963</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8774999999999999</v>
+        <v>1.3283</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4707</v>
+        <v>1.045</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3482</v>
+        <v>0.2833</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5447</v>
+        <v>-1.3783</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2648</v>
+        <v>-0.2988</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8095</v>
+        <v>-1.0795</v>
       </c>
       <c r="P23" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9508</v>
+        <v>-0.9802</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5447</v>
+        <v>-0.7187</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4061</v>
+        <v>-0.2615</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.014</v>
+        <v>-3.7314</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2119</v>
+        <v>-2.0097</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8021</v>
+        <v>-1.7217</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3641</v>
@@ -2326,13 +2326,13 @@
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6266</v>
+        <v>-1.344</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.271</v>
+        <v>-1.0687</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3556</v>
+        <v>-0.2753</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2186</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.3321</v>
+        <v>7.6803</v>
       </c>
       <c r="E25" t="n">
-        <v>13.7941</v>
+        <v>13.7943</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.4619</v>
+        <v>-6.1138</v>
       </c>
       <c r="G25" t="n">
-        <v>3.420099999999999</v>
+        <v>3.4201</v>
       </c>
       <c r="H25" t="n">
         <v>6.115399999999999</v>
@@ -2380,16 +2380,16 @@
         <v>13.0838</v>
       </c>
       <c r="K25" t="n">
-        <v>7.008000000000001</v>
+        <v>7.008</v>
       </c>
       <c r="L25" t="n">
-        <v>6.0757</v>
+        <v>6.075699999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-9.6638</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8927</v>
+        <v>-0.8926999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-8.7712</v>
@@ -2404,13 +2404,13 @@
         <v>11.7205</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1872</v>
+        <v>-0.8392000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3151999999999999</v>
+        <v>-0.3152</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8719</v>
+        <v>-0.5239</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7145</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484201_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484201_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3327</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.2108</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2856</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.8285</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3991</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.932300000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.2224</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1796,6 +1872,11 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,11 +2122,16 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8525</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7536</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6061</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2362</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.34</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5762</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4145</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8366</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>3.2511</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1783</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5034</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.952</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7661</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1858</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2226,72 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1388</v>
+        <v>-0.8525</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0177</v>
+        <v>0.7536</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1211</v>
+        <v>-1.6061</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4222</v>
+        <v>1.2362</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7355</v>
+        <v>-1.34</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1577</v>
+        <v>2.5762</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8774999999999999</v>
+        <v>2.4145</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4707</v>
+        <v>-0.8366</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>3.2511</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5447</v>
+        <v>-1.1783</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2648</v>
+        <v>-0.5034</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8095</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3026</v>
+        <v>-0.952</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1402</v>
+        <v>-0.7661</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1624</v>
+        <v>-0.1858</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2265,11 +2371,16 @@
       <c r="X23" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7314</v>
+        <v>-1.4458</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0097</v>
+        <v>-1.3247</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7217</v>
+        <v>-0.1211</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3641</v>
+        <v>-1.7292</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4429</v>
+        <v>0.4285</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8069</v>
+        <v>-2.1577</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0461</v>
+        <v>-1.1845</v>
       </c>
       <c r="K24" t="n">
-        <v>1.086</v>
+        <v>0.1637</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1321</v>
+        <v>-1.3482</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.318</v>
+        <v>-0.5447</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6431</v>
+        <v>0.2648</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.8095</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.344</v>
+        <v>-0.3026</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0687</v>
+        <v>-0.1402</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2753</v>
+        <v>-0.1624</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.6803</v>
+        <v>-3.7314</v>
       </c>
       <c r="E25" t="n">
+        <v>-2.0097</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.7217</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.3641</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.8069</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.1321</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.318</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6431</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.344</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1.0687</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2753</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484201_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.680299999999998</v>
+      </c>
+      <c r="E26" t="n">
         <v>13.7943</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-6.1138</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>3.4201</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>6.115399999999999</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-2.6954</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>13.0838</v>
       </c>
-      <c r="K25" t="n">
-        <v>7.008</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.075699999999999</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="K26" t="n">
+        <v>7.008000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.0757</v>
+      </c>
+      <c r="M26" t="n">
         <v>-9.6638</v>
       </c>
-      <c r="N25" t="n">
-        <v>-0.8926999999999999</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="N26" t="n">
+        <v>-0.8927</v>
+      </c>
+      <c r="O26" t="n">
         <v>-8.7712</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>7.813700000000001</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-3.9069</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>11.7205</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-0.8392000000000002</v>
       </c>
-      <c r="T25" t="n">
-        <v>-0.3152</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="T26" t="n">
+        <v>-0.3152000000000001</v>
+      </c>
+      <c r="U26" t="n">
         <v>-0.5239</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-2.7145</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>4.932099999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-7.646799999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
